--- a/ressources/Squelette Prjet.xlsx
+++ b/ressources/Squelette Prjet.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\lenak\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\xampp\htdocs\EnseignementSuperieur\ressources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{06A35ECA-C5EA-4944-82BA-1B81068DFB83}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A62AA571-EAB2-4F84-8823-C9CBED310117}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{9289B49A-2C63-4256-91AE-55ED75D7450E}"/>
+    <workbookView xWindow="-105" yWindow="0" windowWidth="14610" windowHeight="15585" xr2:uid="{9289B49A-2C63-4256-91AE-55ED75D7450E}"/>
   </bookViews>
   <sheets>
     <sheet name="Feuil1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="84" uniqueCount="52">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="85" uniqueCount="53">
   <si>
     <t>Quoi ?</t>
   </si>
@@ -44,15 +44,6 @@
     <t>Quelle page ?</t>
   </si>
   <si>
-    <t>Temps (en h)</t>
-  </si>
-  <si>
-    <t>Semaines</t>
-  </si>
-  <si>
-    <t>BDD</t>
-  </si>
-  <si>
     <t>Back</t>
   </si>
   <si>
@@ -192,6 +183,18 @@
   </si>
   <si>
     <t>Liste provenant de la BDD</t>
+  </si>
+  <si>
+    <t>Temps estimé (en h)</t>
+  </si>
+  <si>
+    <t>Création de la BDD</t>
+  </si>
+  <si>
+    <t>Veille connexion BDD site web</t>
+  </si>
+  <si>
+    <t>Rédaction des issues</t>
   </si>
 </sst>
 </file>
@@ -245,10 +248,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -568,16 +567,17 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7F394B27-5784-44B6-B67D-118FA3C814D2}">
-  <dimension ref="A1:D41"/>
+  <dimension ref="A1:C43"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="41" customWidth="1"/>
     <col min="2" max="2" width="28.28515625" customWidth="1"/>
-    <col min="3" max="3" width="13.42578125" customWidth="1"/>
+    <col min="3" max="3" width="19.5703125" customWidth="1"/>
     <col min="4" max="4" width="13.28515625" customWidth="1"/>
+    <col min="6" max="6" width="13.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -585,172 +585,169 @@
         <v>1</v>
       </c>
       <c r="C1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>4</v>
+        <v>50</v>
       </c>
       <c r="B2" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="C2">
         <v>4</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="B3" t="s">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="C3">
         <v>0.75</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="B4" t="s">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="C4">
         <v>1.5</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="B5" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="C5">
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="B6" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="C6">
         <v>4</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="B7" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="C7">
         <v>0.25</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="B8" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C8">
         <v>3</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="B9" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="C9">
         <v>2</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="B10" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="C10">
         <v>4</v>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="B11" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="C11">
         <v>3</v>
       </c>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="B12" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="C12">
         <v>4</v>
       </c>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="B13" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="C13">
         <v>1.5</v>
       </c>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="B14" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="C14">
         <v>3</v>
       </c>
     </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="B15" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="C15">
         <v>2.5</v>
       </c>
     </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="B16" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="C16">
         <v>1</v>
@@ -758,10 +755,10 @@
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="B17" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="C17">
         <v>3</v>
@@ -769,10 +766,10 @@
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="B18" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="C18">
         <v>1</v>
@@ -780,10 +777,10 @@
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="B19" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="C19">
         <v>1</v>
@@ -791,10 +788,10 @@
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="B20" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="C20">
         <v>1</v>
@@ -802,10 +799,10 @@
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="B21" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="C21">
         <v>3</v>
@@ -813,10 +810,10 @@
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="B22" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="C22">
         <v>1.5</v>
@@ -824,10 +821,10 @@
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="B23" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="C23">
         <v>3</v>
@@ -835,10 +832,10 @@
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="B24" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="C24">
         <v>1</v>
@@ -846,10 +843,10 @@
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="B25" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="C25">
         <v>2.5</v>
@@ -857,10 +854,10 @@
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="B26" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="C26">
         <v>1</v>
@@ -868,10 +865,10 @@
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="B27" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="C27">
         <v>2</v>
@@ -879,10 +876,10 @@
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="B28" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="C28">
         <v>2</v>
@@ -890,10 +887,10 @@
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="B29" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="C29">
         <v>2</v>
@@ -901,10 +898,10 @@
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="B30" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="C30">
         <v>3</v>
@@ -912,10 +909,10 @@
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="B31" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="C31">
         <v>1</v>
@@ -923,10 +920,10 @@
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="B32" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="C32">
         <v>1</v>
@@ -934,10 +931,10 @@
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="B33" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="C33">
         <v>2</v>
@@ -945,10 +942,10 @@
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="B34" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="C34">
         <v>1</v>
@@ -956,10 +953,10 @@
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="B35" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="C35">
         <v>2</v>
@@ -967,10 +964,10 @@
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="B36" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="C36">
         <v>2</v>
@@ -978,10 +975,10 @@
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="B37" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="C37">
         <v>2</v>
@@ -989,10 +986,10 @@
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="B38" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="C38">
         <v>3</v>
@@ -1000,10 +997,10 @@
     </row>
     <row r="39" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="B39" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="C39">
         <v>3</v>
@@ -1011,10 +1008,10 @@
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="B40" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="C40">
         <v>3</v>
@@ -1022,13 +1019,29 @@
     </row>
     <row r="41" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="B41" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="C41">
         <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A42" t="s">
+        <v>51</v>
+      </c>
+      <c r="C42">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="43" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A43" t="s">
+        <v>52</v>
+      </c>
+      <c r="C43">
+        <v>4</v>
       </c>
     </row>
   </sheetData>
@@ -1037,6 +1050,21 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100875CF4D41AB6D2409A5BA134E78B9E42" ma:contentTypeVersion="1" ma:contentTypeDescription="Crée un document." ma:contentTypeScope="" ma:versionID="987d2375e1aa7e5b3c3d3a9f8dc9e90d">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns3="a0308db3-8c21-4eba-bd28-4114843e291b" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="3eb3843b39730996179047a7e2a43d60" ns3:_="">
     <xsd:import namespace="a0308db3-8c21-4eba-bd28-4114843e291b"/>
@@ -1162,22 +1190,31 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{88D1B06E-3D00-4009-8FCB-176A42714ECA}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="a0308db3-8c21-4eba-bd28-4114843e291b"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{67767696-35D8-426B-A51D-A65032437CBC}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F0726B72-C296-41E3-AEB8-64C259EDC63E}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -1193,28 +1230,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{67767696-35D8-426B-A51D-A65032437CBC}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{88D1B06E-3D00-4009-8FCB-176A42714ECA}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="a0308db3-8c21-4eba-bd28-4114843e291b"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>